--- a/data dipake.xlsx
+++ b/data dipake.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DINDA\Documents\datmin asekk\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DINDA\Documents\datmin asekk\fix bgt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5AE5E41-88C4-4578-8D15-560A35587F4C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2261FC9B-1BEF-43DD-8790-1B124D3E228A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3000" yWindow="3000" windowWidth="17280" windowHeight="9960" xr2:uid="{6BAA4198-5FC7-4C3C-A988-0E24832A444F}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{6BAA4198-5FC7-4C3C-A988-0E24832A444F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="42">
   <si>
     <t>no</t>
   </si>
@@ -115,18 +115,6 @@
   </si>
   <si>
     <t>satuan juta rupiah, nama probvinsi dan huruf kapital</t>
-  </si>
-  <si>
-    <t>jumlah UMKM per provinsi non pertanian</t>
-  </si>
-  <si>
-    <t>PERKEMBANGAN_DATA_UMKM_NON_PERTANIAN_TAHUN_2024_2025_SIDT_UMKM_1177b5d58d (1)</t>
-  </si>
-  <si>
-    <t>kolom jumlah 2025</t>
-  </si>
-  <si>
-    <t>2024-25</t>
   </si>
   <si>
     <t>masih pdf</t>
@@ -709,23 +697,13 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -733,19 +711,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2">
         <v>2024</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -753,13 +731,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2">
         <v>2024</v>
@@ -771,19 +749,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E11" s="2">
         <v>2024</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -791,13 +769,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E12" s="3">
         <v>2024</v>
